--- a/TDXapp/tdxAppData/akEMP.xlsx
+++ b/TDXapp/tdxAppData/akEMP.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B607"/>
+  <dimension ref="A1:B381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000170</t>
+          <t>399415</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000847</t>
+          <t>399416</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000849</t>
+          <t>399679</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000851</t>
+          <t>930791</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000854</t>
+          <t>930796</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000856</t>
+          <t>930820</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>000857</t>
+          <t>930846</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>000858</t>
+          <t>930850</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>000865</t>
+          <t>930851</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>399415</t>
+          <t>930875</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>399416</t>
+          <t>930882</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>399629</t>
+          <t>930901</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>399630</t>
+          <t>930902</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>399631</t>
+          <t>930910</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>399632</t>
+          <t>930917</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>399633</t>
+          <t>930927</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>399635</t>
+          <t>930928</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>399636</t>
+          <t>930937</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>399637</t>
+          <t>930938</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>399638</t>
+          <t>930939</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>399639</t>
+          <t>930949</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>399640</t>
+          <t>930955</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>399641</t>
+          <t>930986</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>399642</t>
+          <t>930997</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>399643</t>
+          <t>930999</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>399644</t>
+          <t>931000</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>399645</t>
+          <t>931008</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>399646</t>
+          <t>931009</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>399647</t>
+          <t>931021</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>399648</t>
+          <t>931023</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>399649</t>
+          <t>931033</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>399650</t>
+          <t>931039</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>399651</t>
+          <t>931052</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>399652</t>
+          <t>931053</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>399653</t>
+          <t>931066</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>399654</t>
+          <t>931067</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>399655</t>
+          <t>931068</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>399656</t>
+          <t>931069</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>399657</t>
+          <t>931071</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>399658</t>
+          <t>931079</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>399659</t>
+          <t>931087</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>399660</t>
+          <t>931088</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>399661</t>
+          <t>931127</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>399662</t>
+          <t>931132</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>399663</t>
+          <t>931133</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>399664</t>
+          <t>931134</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>399665</t>
+          <t>931136</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>399666</t>
+          <t>931139</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>399667</t>
+          <t>931140</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>399668</t>
+          <t>931141</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>399669</t>
+          <t>931142</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>399670</t>
+          <t>931144</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>399671</t>
+          <t>931151</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>399672</t>
+          <t>931152</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>399673</t>
+          <t>931157</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>399674</t>
+          <t>931159</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>399675</t>
+          <t>931160</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>399676</t>
+          <t>931163</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>399677</t>
+          <t>931165</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>399678</t>
+          <t>931166</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>399679</t>
+          <t>931167</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>399680</t>
+          <t>931186</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>399681</t>
+          <t>931187</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>399682</t>
+          <t>931230</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>399683</t>
+          <t>931231</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>399684</t>
+          <t>931232</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>399685</t>
+          <t>931234</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>399686</t>
+          <t>931235</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>399687</t>
+          <t>931238</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>399688</t>
+          <t>931243</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>399689</t>
+          <t>931247</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>399692</t>
+          <t>931248</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>399693</t>
+          <t>931258</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>399694</t>
+          <t>931268</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>399695</t>
+          <t>931271</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>399696</t>
+          <t>931357</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>399697</t>
+          <t>931372</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>399698</t>
+          <t>931373</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>399699</t>
+          <t>931375</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>399701</t>
+          <t>931380</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>399702</t>
+          <t>931381</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>399703</t>
+          <t>931382</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>399704</t>
+          <t>931393</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>399705</t>
+          <t>931395</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>399706</t>
+          <t>931402</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>399707</t>
+          <t>931403</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>399750</t>
+          <t>931404</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>399802</t>
+          <t>931406</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>399803</t>
+          <t>931409</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>399804</t>
+          <t>931412</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>399805</t>
+          <t>931440</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>399806</t>
+          <t>931442</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>399807</t>
+          <t>931446</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>399808</t>
+          <t>931447</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>399809</t>
+          <t>931456</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>399810</t>
+          <t>931461</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>399811</t>
+          <t>931463</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>399812</t>
+          <t>931465</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>399813</t>
+          <t>931468</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>399814</t>
+          <t>931469</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>399850</t>
+          <t>931470</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>399852</t>
+          <t>931476</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>399901</t>
+          <t>931477</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>399903</t>
+          <t>931478</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>399905</t>
+          <t>931479</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>399913</t>
+          <t>931480</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>399914</t>
+          <t>931481</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>399928</t>
+          <t>931484</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>399932</t>
+          <t>931487</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>399933</t>
+          <t>931494</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>399934</t>
+          <t>931495</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>399935</t>
+          <t>931521</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>399959</t>
+          <t>931522</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>399965</t>
+          <t>931523</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>399966</t>
+          <t>931524</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>399967</t>
+          <t>931526</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>399970</t>
+          <t>931529</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>399971</t>
+          <t>931554</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>399972</t>
+          <t>931559</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>399973</t>
+          <t>931575</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>399974</t>
+          <t>931579</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>399975</t>
+          <t>931580</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>399976</t>
+          <t>931581</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>399983</t>
+          <t>931582</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>399986</t>
+          <t>931583</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>931585</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>399989</t>
+          <t>931586</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>399990</t>
+          <t>931587</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>399991</t>
+          <t>931588</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>399992</t>
+          <t>931589</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>399993</t>
+          <t>931590</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>399994</t>
+          <t>931591</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>399995</t>
+          <t>931593</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>399996</t>
+          <t>931594</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>399997</t>
+          <t>931596</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>399998</t>
+          <t>931598</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>899003</t>
+          <t>931599</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>899050</t>
+          <t>931643</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>899601</t>
+          <t>931646</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>930050</t>
+          <t>931647</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>930598</t>
+          <t>931648</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>930599</t>
+          <t>931652</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>930601</t>
+          <t>931663</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>930604</t>
+          <t>931672</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>930606</t>
+          <t>931687</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>930608</t>
+          <t>931695</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>930614</t>
+          <t>931696</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>930620</t>
+          <t>931697</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>930621</t>
+          <t>931698</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>930622</t>
+          <t>931718</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>930625</t>
+          <t>931719</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>930629</t>
+          <t>931725</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>930632</t>
+          <t>931733</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>930633</t>
+          <t>931743</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>930640</t>
+          <t>931746</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>930641</t>
+          <t>931752</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>930648</t>
+          <t>931755</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>930651</t>
+          <t>931772</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>930652</t>
+          <t>931775</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>930653</t>
+          <t>931778</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>930660</t>
+          <t>931791</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>930661</t>
+          <t>931792</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>930662</t>
+          <t>931793</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>930697</t>
+          <t>931798</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>930701</t>
+          <t>931799</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>930703</t>
+          <t>931802</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>930707</t>
+          <t>931823</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>930708</t>
+          <t>931834</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>930712</t>
+          <t>931837</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>930713</t>
+          <t>931848</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>930715</t>
+          <t>931852</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>930716</t>
+          <t>931855</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>930719</t>
+          <t>931865</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>930720</t>
+          <t>931866</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>930721</t>
+          <t>931892</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>930723</t>
+          <t>931897</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>930725</t>
+          <t>931992</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>930726</t>
+          <t>931994</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>930734</t>
+          <t>932000</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>930738</t>
+          <t>932004</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>930740</t>
+          <t>932037</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>930743</t>
+          <t>932038</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>930758</t>
+          <t>932039</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>930767</t>
+          <t>932042</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>930781</t>
+          <t>932046</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>930782</t>
+          <t>932052</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>930790</t>
+          <t>932056</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>930791</t>
+          <t>932066</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>930796</t>
+          <t>932068</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>930820</t>
+          <t>932075</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>930821</t>
+          <t>932076</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>930835</t>
+          <t>932077</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>930838</t>
+          <t>932078</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>930846</t>
+          <t>932079</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>930850</t>
+          <t>932080</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>930851</t>
+          <t>932081</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>930875</t>
+          <t>932082</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>930882</t>
+          <t>932083</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>930901</t>
+          <t>932084</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>930902</t>
+          <t>932085</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>930910</t>
+          <t>932086</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>930917</t>
+          <t>932087</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>930927</t>
+          <t>932094</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>930928</t>
+          <t>932217</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>930937</t>
+          <t>932257</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>930938</t>
+          <t>932263</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>930939</t>
+          <t>932266</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>930949</t>
+          <t>932305</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>930955</t>
+          <t>932306</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>930984</t>
+          <t>932308</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>930986</t>
+          <t>932315</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>930997</t>
+          <t>932357</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>930999</t>
+          <t>932359</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>931000</t>
+          <t>932365</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>931008</t>
+          <t>932366</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>931009</t>
+          <t>932367</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>931021</t>
+          <t>932368</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>931023</t>
+          <t>932419</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>931033</t>
+          <t>932420</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>931039</t>
+          <t>932422</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>931052</t>
+          <t>932536</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>950090</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>931065</t>
+          <t>950092</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>931066</t>
+          <t>970070</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>931067</t>
+          <t>980001</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>931068</t>
+          <t>980015</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>931069</t>
+          <t>980016</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>931070</t>
+          <t>980017</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>931071</t>
+          <t>980018</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>931079</t>
+          <t>980022</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>931086</t>
+          <t>980023</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>931087</t>
+          <t>980027</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>931088</t>
+          <t>980028</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>931127</t>
+          <t>980030</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>931132</t>
+          <t>980032</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>931133</t>
+          <t>980035</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>931134</t>
+          <t>980068</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>931136</t>
+          <t>980076</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>931139</t>
+          <t>980092</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>931140</t>
+          <t>H11030</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>931141</t>
+          <t>H11031</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>931142</t>
+          <t>H11041</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>931144</t>
+          <t>H11042</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>931151</t>
+          <t>H11043</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>931152</t>
+          <t>H11044</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>931157</t>
+          <t>H11045</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>931159</t>
+          <t>H11046</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>931160</t>
+          <t>H11047</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>931163</t>
+          <t>H11049</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>931165</t>
+          <t>H11050</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>931166</t>
+          <t>H11052</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>931167</t>
+          <t>H11054</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>931186</t>
+          <t>H11057</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>931187</t>
+          <t>H11059</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>931230</t>
+          <t>H11121</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>931231</t>
+          <t>H11136</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>931232</t>
+          <t>H30007</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>931234</t>
+          <t>H30015</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>931235</t>
+          <t>H30022</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>931238</t>
+          <t>H30031</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>931243</t>
+          <t>H30035</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>931247</t>
+          <t>H30036</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>931248</t>
+          <t>H30037</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>931258</t>
+          <t>H30038</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>931268</t>
+          <t>H30039</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>931271</t>
+          <t>H30040</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>931357</t>
+          <t>H30041</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>931372</t>
+          <t>H30042</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>931373</t>
+          <t>H30043</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>931374</t>
+          <t>H30044</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>931375</t>
+          <t>H30045</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>931380</t>
+          <t>H30046</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>931381</t>
+          <t>H30047</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>931382</t>
+          <t>H30048</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>931393</t>
+          <t>H30049</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>931395</t>
+          <t>H30050</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>931402</t>
+          <t>H30051</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>931403</t>
+          <t>H30052</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>931404</t>
+          <t>H30053</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>931406</t>
+          <t>H30054</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>931409</t>
+          <t>H30055</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>931412</t>
+          <t>H30056</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>931440</t>
+          <t>H30057</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>931442</t>
+          <t>H30058</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>931446</t>
+          <t>H30059</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>931447</t>
+          <t>H30060</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>931456</t>
+          <t>H30061</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>931461</t>
+          <t>H30062</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>931463</t>
+          <t>H30063</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>931465</t>
+          <t>H30064</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>931468</t>
+          <t>H30065</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>931469</t>
+          <t>H30066</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>931470</t>
+          <t>H30067</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>931476</t>
+          <t>H30082</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>931477</t>
+          <t>H30083</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>931478</t>
+          <t>H30086</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>931479</t>
+          <t>H30089</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>931480</t>
+          <t>H30094</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>931481</t>
+          <t>H30124</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>931484</t>
+          <t>H30171</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>931487</t>
+          <t>H30178</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>931494</t>
+          <t>H30182</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>931495</t>
+          <t>H30184</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>931496</t>
+          <t>H30198</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>931520</t>
+          <t>H30199</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>931521</t>
+          <t>H30202</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>931522</t>
+          <t>H30205</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>931523</t>
+          <t>H30217</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>931524</t>
+          <t>H30251</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>931526</t>
+          <t>H30252</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>931529</t>
+          <t>H30255</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>931554</t>
+          <t>H30257</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>931559</t>
+          <t>H30263</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>931575</t>
+          <t>H30269</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>931579</t>
+          <t>H30270</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>931580</t>
+          <t>H30318</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>931581</t>
+          <t>H30344</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>931582</t>
+          <t>H30352</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>931583</t>
+          <t>H30356</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>931585</t>
+          <t>H30359</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>931586</t>
+          <t>H30362</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>931587</t>
+          <t>H30365</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>931588</t>
+          <t>H30366</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>931589</t>
+          <t>H30372</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>931590</t>
+          <t>H30373</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>931591</t>
+          <t>H30455</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>931593</t>
+          <t>H30463</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>931594</t>
+          <t>H30531</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>931596</t>
+          <t>H30533</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>931598</t>
+          <t>H30535</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>931599</t>
+          <t>H30537</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>931643</t>
+          <t>H30552</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>931646</t>
+          <t>H30588</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>931647</t>
+          <t>H30590</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>931648</t>
+          <t>H30597</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>931652</t>
+          <t>H50001</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>931654</t>
+          <t>H50002</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>931655</t>
+          <t>H50003</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>931663</t>
+          <t>H50004</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>931672</t>
+          <t>H50005</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>931687</t>
+          <t>H50006</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>931695</t>
+          <t>H50007</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>931696</t>
+          <t>H50008</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>931697</t>
+          <t>H50009</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>931698</t>
+          <t>H50010</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>931718</t>
+          <t>H50011</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>931719</t>
+          <t>H50012</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>931722</t>
+          <t>H50013</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>931725</t>
+          <t>H50014</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>931733</t>
+          <t>H50015</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>931743</t>
+          <t>H50016</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>931746</t>
+          <t>H50017</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>931752</t>
+          <t>H50018</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>931755</t>
+          <t>H50019</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>931772</t>
+          <t>H50020</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>931775</t>
+          <t>H50021</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>931778</t>
+          <t>H50022</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>931791</t>
+          <t>H50023</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>931792</t>
+          <t>H50024</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>931793</t>
+          <t>H50025</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>931798</t>
+          <t>H50026</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>931799</t>
+          <t>H50027</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>931802</t>
+          <t>H50028</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>931823</t>
+          <t>H50029</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>931834</t>
+          <t>H50030</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>931837</t>
+          <t>H50031</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>931840</t>
+          <t>H50032</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>931841</t>
+          <t>H50033</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>931842</t>
+          <t>H50034</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>931848</t>
+          <t>H50035</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>931852</t>
+          <t>H50036</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>931855</t>
+          <t>H50037</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>931865</t>
+          <t>H50038</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>931866</t>
+          <t>H50039</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>931877</t>
+          <t>H50040</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>931892</t>
+          <t>H50042</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>931897</t>
+          <t>H50052</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>931992</t>
+          <t>H50053</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>931994</t>
+          <t>H50054</t>
         </is>
       </c>
     </row>
@@ -4231,2267 +4231,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>932000</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="1" t="n">
-        <v>380</v>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>932004</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="1" t="n">
-        <v>381</v>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>932021</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="1" t="n">
-        <v>382</v>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>932022</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="1" t="n">
-        <v>383</v>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>932023</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="1" t="n">
-        <v>384</v>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>932037</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="1" t="n">
-        <v>385</v>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>932038</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="1" t="n">
-        <v>386</v>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>932039</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="1" t="n">
-        <v>387</v>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>932042</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="1" t="n">
-        <v>388</v>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>932046</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" s="1" t="n">
-        <v>389</v>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>932047</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="1" t="n">
-        <v>390</v>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>932049</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" s="1" t="n">
-        <v>391</v>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>932052</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" s="1" t="n">
-        <v>392</v>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>932056</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" s="1" t="n">
-        <v>393</v>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>932066</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="1" t="n">
-        <v>394</v>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>932068</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="1" t="n">
-        <v>395</v>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>932075</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" s="1" t="n">
-        <v>396</v>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>932076</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="1" t="n">
-        <v>397</v>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>932077</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="1" t="n">
-        <v>398</v>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>932078</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" s="1" t="n">
-        <v>399</v>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>932079</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" s="1" t="n">
-        <v>400</v>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>932080</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" s="1" t="n">
-        <v>401</v>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>932081</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="1" t="n">
-        <v>402</v>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>932082</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="1" t="n">
-        <v>403</v>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>932083</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="1" t="n">
-        <v>404</v>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>932084</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="1" t="n">
-        <v>405</v>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>932085</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="1" t="n">
-        <v>406</v>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>932086</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="1" t="n">
-        <v>407</v>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>932087</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="1" t="n">
-        <v>408</v>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>932094</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="1" t="n">
-        <v>409</v>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>932217</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="1" t="n">
-        <v>410</v>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>932257</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="1" t="n">
-        <v>411</v>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>932258</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="1" t="n">
-        <v>412</v>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>932263</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" s="1" t="n">
-        <v>413</v>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>932266</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" s="1" t="n">
-        <v>414</v>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>932305</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" s="1" t="n">
-        <v>415</v>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>932306</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" s="1" t="n">
-        <v>416</v>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>932307</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" s="1" t="n">
-        <v>417</v>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>932308</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" s="1" t="n">
-        <v>418</v>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>932315</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" s="1" t="n">
-        <v>419</v>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>932357</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="1" t="n">
-        <v>420</v>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>932359</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" s="1" t="n">
-        <v>421</v>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>932365</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" s="1" t="n">
-        <v>422</v>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>932366</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="1" t="n">
-        <v>423</v>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>932367</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" s="1" t="n">
-        <v>424</v>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>932368</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" s="1" t="n">
-        <v>425</v>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>932419</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="1" t="n">
-        <v>426</v>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>932420</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" s="1" t="n">
-        <v>427</v>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>932536</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="1" t="n">
-        <v>428</v>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>950090</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" s="1" t="n">
-        <v>429</v>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>950092</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="1" t="n">
-        <v>430</v>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>970070</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" s="1" t="n">
-        <v>431</v>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>980001</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" s="1" t="n">
-        <v>432</v>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>980015</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" s="1" t="n">
-        <v>433</v>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>980016</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" s="1" t="n">
-        <v>434</v>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>980017</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" s="1" t="n">
-        <v>435</v>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>980018</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" s="1" t="n">
-        <v>436</v>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>980022</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" s="1" t="n">
-        <v>437</v>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>980023</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" s="1" t="n">
-        <v>438</v>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>980027</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" s="1" t="n">
-        <v>439</v>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>980028</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" s="1" t="n">
-        <v>440</v>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>980030</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" s="1" t="n">
-        <v>441</v>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>980032</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" s="1" t="n">
-        <v>442</v>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>980035</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" s="1" t="n">
-        <v>443</v>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>980068</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" s="1" t="n">
-        <v>444</v>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>980076</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" s="1" t="n">
-        <v>445</v>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>980092</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" s="1" t="n">
-        <v>446</v>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>988006</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" s="1" t="n">
-        <v>447</v>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>988007</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" s="1" t="n">
-        <v>448</v>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>988106</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>988107</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" s="1" t="n">
-        <v>450</v>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>988201</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" s="1" t="n">
-        <v>451</v>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>990001</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" s="1" t="n">
-        <v>452</v>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>CES100</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" s="1" t="n">
-        <v>453</v>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>CES120</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" s="1" t="n">
-        <v>454</v>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>CES280</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" s="1" t="n">
-        <v>455</v>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>CES300</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" s="1" t="n">
-        <v>456</v>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>CESA80</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" s="1" t="n">
-        <v>457</v>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>CESCPD</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" s="1" t="n">
-        <v>458</v>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>CESFHY</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" s="1" t="n">
-        <v>459</v>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>CESG10</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" s="1" t="n">
-        <v>460</v>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>CESHKB</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" s="1" t="n">
-        <v>461</v>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>CESHKM</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" s="1" t="n">
-        <v>462</v>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>CESP50</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" s="1" t="n">
-        <v>463</v>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>H11030</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" s="1" t="n">
-        <v>464</v>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>H11031</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" s="1" t="n">
-        <v>465</v>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>H11041</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" s="1" t="n">
-        <v>466</v>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>H11042</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" s="1" t="n">
-        <v>467</v>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>H11043</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" s="1" t="n">
-        <v>468</v>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>H11044</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" s="1" t="n">
-        <v>469</v>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>H11045</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" s="1" t="n">
-        <v>470</v>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>H11046</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" s="1" t="n">
-        <v>471</v>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>H11047</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" s="1" t="n">
-        <v>472</v>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>H11049</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" s="1" t="n">
-        <v>473</v>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>H11050</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" s="1" t="n">
-        <v>474</v>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>H11052</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" s="1" t="n">
-        <v>475</v>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>H11054</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" s="1" t="n">
-        <v>476</v>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>H11057</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" s="1" t="n">
-        <v>477</v>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>H11059</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" s="1" t="n">
-        <v>478</v>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>H11121</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" s="1" t="n">
-        <v>479</v>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>H11136</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" s="1" t="n">
-        <v>480</v>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>H30007</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" s="1" t="n">
-        <v>481</v>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>H30015</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" s="1" t="n">
-        <v>482</v>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>H30022</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" s="1" t="n">
-        <v>483</v>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>H30031</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" s="1" t="n">
-        <v>484</v>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>H30035</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" s="1" t="n">
-        <v>485</v>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>H30036</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" s="1" t="n">
-        <v>486</v>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>H30037</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" s="1" t="n">
-        <v>487</v>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>H30038</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" s="1" t="n">
-        <v>488</v>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>H30039</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" s="1" t="n">
-        <v>489</v>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>H30040</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" s="1" t="n">
-        <v>490</v>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>H30041</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" s="1" t="n">
-        <v>491</v>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>H30042</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" s="1" t="n">
-        <v>492</v>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>H30043</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" s="1" t="n">
-        <v>493</v>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>H30044</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" s="1" t="n">
-        <v>494</v>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>H30045</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" s="1" t="n">
-        <v>495</v>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>H30046</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" s="1" t="n">
-        <v>496</v>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>H30047</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" s="1" t="n">
-        <v>497</v>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>H30048</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" s="1" t="n">
-        <v>498</v>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>H30049</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" s="1" t="n">
-        <v>499</v>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>H30050</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>H30051</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" s="1" t="n">
-        <v>501</v>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>H30052</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" s="1" t="n">
-        <v>502</v>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>H30053</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" s="1" t="n">
-        <v>503</v>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>H30054</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" s="1" t="n">
-        <v>504</v>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>H30055</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" s="1" t="n">
-        <v>505</v>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>H30056</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" s="1" t="n">
-        <v>506</v>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>H30057</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" s="1" t="n">
-        <v>507</v>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>H30058</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" s="1" t="n">
-        <v>508</v>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>H30059</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" s="1" t="n">
-        <v>509</v>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>H30060</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" s="1" t="n">
-        <v>510</v>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>H30061</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" s="1" t="n">
-        <v>511</v>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>H30062</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" s="1" t="n">
-        <v>512</v>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>H30063</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" s="1" t="n">
-        <v>513</v>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>H30064</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" s="1" t="n">
-        <v>514</v>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>H30065</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" s="1" t="n">
-        <v>515</v>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>H30066</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" s="1" t="n">
-        <v>516</v>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>H30067</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" s="1" t="n">
-        <v>517</v>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>H30082</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" s="1" t="n">
-        <v>518</v>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>H30083</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" s="1" t="n">
-        <v>519</v>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>H30086</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" s="1" t="n">
-        <v>520</v>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>H30089</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" s="1" t="n">
-        <v>521</v>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>H30094</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" s="1" t="n">
-        <v>522</v>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>H30106</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" s="1" t="n">
-        <v>523</v>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>H30124</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" s="1" t="n">
-        <v>524</v>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>H30171</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" s="1" t="n">
-        <v>525</v>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>H30178</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" s="1" t="n">
-        <v>526</v>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>H30182</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" s="1" t="n">
-        <v>527</v>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>H30184</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" s="1" t="n">
-        <v>528</v>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>H30198</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" s="1" t="n">
-        <v>529</v>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>H30199</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" s="1" t="n">
-        <v>530</v>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>H30202</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" s="1" t="n">
-        <v>531</v>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>H30205</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" s="1" t="n">
-        <v>532</v>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>H30217</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" s="1" t="n">
-        <v>533</v>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>H30251</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" s="1" t="n">
-        <v>534</v>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>H30252</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" s="1" t="n">
-        <v>535</v>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>H30255</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" s="1" t="n">
-        <v>536</v>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>H30257</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" s="1" t="n">
-        <v>537</v>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>H30263</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" s="1" t="n">
-        <v>538</v>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>H30269</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" s="1" t="n">
-        <v>539</v>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>H30270</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" s="1" t="n">
-        <v>540</v>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>H30318</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" s="1" t="n">
-        <v>541</v>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>H30344</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" s="1" t="n">
-        <v>542</v>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>H30352</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" s="1" t="n">
-        <v>543</v>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>H30356</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" s="1" t="n">
-        <v>544</v>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>H30359</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" s="1" t="n">
-        <v>545</v>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>H30362</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" s="1" t="n">
-        <v>546</v>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>H30365</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" s="1" t="n">
-        <v>547</v>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>H30366</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" s="1" t="n">
-        <v>548</v>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>H30372</t>
-        </is>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" s="1" t="n">
-        <v>549</v>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>H30373</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" s="1" t="n">
-        <v>550</v>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>H30455</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" s="1" t="n">
-        <v>551</v>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>H30463</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" s="1" t="n">
-        <v>552</v>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>H30531</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" s="1" t="n">
-        <v>553</v>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>H30533</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" s="1" t="n">
-        <v>554</v>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>H30535</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" s="1" t="n">
-        <v>555</v>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>H30537</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" s="1" t="n">
-        <v>556</v>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>H30552</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" s="1" t="n">
-        <v>557</v>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>H30588</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" s="1" t="n">
-        <v>558</v>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>H30590</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" s="1" t="n">
-        <v>559</v>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>H30597</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" s="1" t="n">
-        <v>560</v>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>H50001</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" s="1" t="n">
-        <v>561</v>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>H50002</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" s="1" t="n">
-        <v>562</v>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>H50003</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" s="1" t="n">
-        <v>563</v>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>H50004</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" s="1" t="n">
-        <v>564</v>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>H50005</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" s="1" t="n">
-        <v>565</v>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>H50006</t>
-        </is>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" s="1" t="n">
-        <v>566</v>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>H50007</t>
-        </is>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" s="1" t="n">
-        <v>567</v>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>H50008</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" s="1" t="n">
-        <v>568</v>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>H50009</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" s="1" t="n">
-        <v>569</v>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>H50010</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" s="1" t="n">
-        <v>570</v>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>H50011</t>
-        </is>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" s="1" t="n">
-        <v>571</v>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>H50012</t>
-        </is>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" s="1" t="n">
-        <v>572</v>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>H50013</t>
-        </is>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" s="1" t="n">
-        <v>573</v>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>H50014</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" s="1" t="n">
-        <v>574</v>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>H50015</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" s="1" t="n">
-        <v>575</v>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>H50016</t>
-        </is>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" s="1" t="n">
-        <v>576</v>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>H50017</t>
-        </is>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" s="1" t="n">
-        <v>577</v>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>H50018</t>
-        </is>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" s="1" t="n">
-        <v>578</v>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>H50019</t>
-        </is>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" s="1" t="n">
-        <v>579</v>
-      </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>H50020</t>
-        </is>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" s="1" t="n">
-        <v>580</v>
-      </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>H50021</t>
-        </is>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" s="1" t="n">
-        <v>581</v>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>H50022</t>
-        </is>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" s="1" t="n">
-        <v>582</v>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>H50023</t>
-        </is>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" s="1" t="n">
-        <v>583</v>
-      </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t>H50024</t>
-        </is>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" s="1" t="n">
-        <v>584</v>
-      </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>H50025</t>
-        </is>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" s="1" t="n">
-        <v>585</v>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>H50026</t>
-        </is>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" s="1" t="n">
-        <v>586</v>
-      </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>H50027</t>
-        </is>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" s="1" t="n">
-        <v>587</v>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>H50028</t>
-        </is>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" s="1" t="n">
-        <v>588</v>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>H50029</t>
-        </is>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" s="1" t="n">
-        <v>589</v>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>H50030</t>
-        </is>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" s="1" t="n">
-        <v>590</v>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>H50031</t>
-        </is>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" s="1" t="n">
-        <v>591</v>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>H50032</t>
-        </is>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" s="1" t="n">
-        <v>592</v>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>H50033</t>
-        </is>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" s="1" t="n">
-        <v>593</v>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>H50034</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" s="1" t="n">
-        <v>594</v>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>H50035</t>
-        </is>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" s="1" t="n">
-        <v>595</v>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>H50036</t>
-        </is>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" s="1" t="n">
-        <v>596</v>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>H50037</t>
-        </is>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" s="1" t="n">
-        <v>597</v>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>H50038</t>
-        </is>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" s="1" t="n">
-        <v>598</v>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>H50039</t>
-        </is>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" s="1" t="n">
-        <v>599</v>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>H50040</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" s="1" t="n">
-        <v>600</v>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>H50042</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" s="1" t="n">
-        <v>601</v>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>H50052</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" s="1" t="n">
-        <v>602</v>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>H50053</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" s="1" t="n">
-        <v>603</v>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>H50054</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" s="1" t="n">
-        <v>604</v>
-      </c>
-      <c r="B606" t="inlineStr">
-        <is>
           <t>H50055</t>
-        </is>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" s="1" t="n">
-        <v>605</v>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>SHHKSI</t>
         </is>
       </c>
     </row>
